--- a/问卷数据.xlsx
+++ b/问卷数据.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leoya\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leoya\Desktop\我的德语二外研究\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="95">
   <si>
     <t>作答ID</t>
   </si>
@@ -311,6 +311,12 @@
   </si>
   <si>
     <t>无</t>
+  </si>
+  <si>
+    <t>5号</t>
+  </si>
+  <si>
+    <t>6号</t>
   </si>
 </sst>
 </file>
@@ -926,9 +932,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1466,891 +1478,1245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BF5"/>
-  <sheetFormatPr defaultColWidth="9.55752212389381" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:BF7"/>
+  <sheetFormatPr defaultColWidth="9.55752212389381" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="9.55752212389381" style="1"/>
-    <col min="3" max="3" width="21.1858407079646" customWidth="1"/>
-    <col min="5" max="5" width="11.6637168141593"/>
+    <col min="1" max="1" width="9.55752212389381" style="2"/>
+    <col min="2" max="2" width="9.55752212389381" style="3"/>
+    <col min="3" max="3" width="21.1858407079646" style="3" customWidth="1"/>
+    <col min="4" max="5" width="11.6637168141593" style="3"/>
+    <col min="6" max="16384" width="9.55752212389381" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:58">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AP1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AT1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AU1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AV1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AW1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AX1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AY1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BA1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BB1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BC1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BD1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BE1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BF1" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:58">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>117.283042</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>31.86119</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="3">
         <v>1</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="3">
         <v>1</v>
       </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>5</v>
-      </c>
-      <c r="Y2">
-        <v>4</v>
-      </c>
-      <c r="Z2">
-        <v>4</v>
-      </c>
-      <c r="AA2">
-        <v>4</v>
-      </c>
-      <c r="AB2">
+      <c r="Q2" s="3">
+        <v>0</v>
+      </c>
+      <c r="R2" s="3">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3">
+        <v>0</v>
+      </c>
+      <c r="T2" s="3">
+        <v>0</v>
+      </c>
+      <c r="U2" s="3">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3">
+        <v>0</v>
+      </c>
+      <c r="X2" s="3">
+        <v>5</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>4</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AB2" s="3">
         <v>3</v>
       </c>
-      <c r="AC2">
-        <v>4</v>
-      </c>
-      <c r="AD2">
-        <v>5</v>
-      </c>
-      <c r="AE2">
+      <c r="AC2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AE2" s="3">
         <v>3</v>
       </c>
-      <c r="AF2">
-        <v>4</v>
-      </c>
-      <c r="AG2">
-        <v>4</v>
-      </c>
-      <c r="AH2">
-        <v>5</v>
-      </c>
-      <c r="AI2">
-        <v>5</v>
-      </c>
-      <c r="AJ2">
-        <v>5</v>
-      </c>
-      <c r="AK2">
-        <v>5</v>
-      </c>
-      <c r="AL2">
-        <v>5</v>
-      </c>
-      <c r="AM2">
-        <v>4</v>
-      </c>
-      <c r="AN2">
-        <v>5</v>
-      </c>
-      <c r="AO2">
-        <v>4</v>
-      </c>
-      <c r="AP2">
-        <v>4</v>
-      </c>
-      <c r="AQ2">
+      <c r="AF2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AJ2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AK2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AL2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AM2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AN2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AO2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AP2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AQ2" s="3">
         <v>6</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AS2">
-        <v>4</v>
-      </c>
-      <c r="AT2">
-        <v>5</v>
-      </c>
-      <c r="AU2">
-        <v>5</v>
-      </c>
-      <c r="AV2">
-        <v>5</v>
-      </c>
-      <c r="AW2">
-        <v>5</v>
-      </c>
-      <c r="AX2">
-        <v>4</v>
-      </c>
-      <c r="AY2">
-        <v>5</v>
-      </c>
-      <c r="AZ2">
-        <v>5</v>
-      </c>
-      <c r="BA2">
+      <c r="AS2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AT2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AU2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AV2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AW2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AX2" s="3">
+        <v>4</v>
+      </c>
+      <c r="AY2" s="3">
+        <v>5</v>
+      </c>
+      <c r="AZ2" s="3">
+        <v>5</v>
+      </c>
+      <c r="BA2" s="3">
         <v>3</v>
       </c>
-      <c r="BB2">
+      <c r="BB2" s="3">
         <v>3</v>
       </c>
-      <c r="BC2">
+      <c r="BC2" s="3">
         <v>3</v>
       </c>
-      <c r="BD2">
-        <v>4</v>
-      </c>
-      <c r="BE2" t="s">
+      <c r="BD2" s="3">
+        <v>4</v>
+      </c>
+      <c r="BE2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BF2" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:58">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>117.283042</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>31.86119</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="3">
         <v>1</v>
       </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>4</v>
-      </c>
-      <c r="Y3">
+      <c r="P3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0</v>
+      </c>
+      <c r="R3" s="3">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3">
+        <v>0</v>
+      </c>
+      <c r="U3" s="3">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3">
+        <v>0</v>
+      </c>
+      <c r="W3" s="3">
+        <v>0</v>
+      </c>
+      <c r="X3" s="3">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="3">
         <v>2</v>
       </c>
-      <c r="Z3">
-        <v>4</v>
-      </c>
-      <c r="AA3">
+      <c r="Z3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="3">
         <v>2</v>
       </c>
-      <c r="AB3">
+      <c r="AB3" s="3">
         <v>1</v>
       </c>
-      <c r="AC3">
-        <v>4</v>
-      </c>
-      <c r="AD3">
-        <v>4</v>
-      </c>
-      <c r="AE3">
-        <v>4</v>
-      </c>
-      <c r="AF3">
-        <v>5</v>
-      </c>
-      <c r="AG3">
-        <v>4</v>
-      </c>
-      <c r="AH3">
+      <c r="AC3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>5</v>
+      </c>
+      <c r="AG3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AH3" s="3">
         <v>6</v>
       </c>
-      <c r="AI3">
-        <v>4</v>
-      </c>
-      <c r="AJ3">
-        <v>4</v>
-      </c>
-      <c r="AK3">
-        <v>5</v>
-      </c>
-      <c r="AL3">
-        <v>4</v>
-      </c>
-      <c r="AM3">
-        <v>4</v>
-      </c>
-      <c r="AN3">
-        <v>4</v>
-      </c>
-      <c r="AO3">
-        <v>4</v>
-      </c>
-      <c r="AP3">
-        <v>4</v>
-      </c>
-      <c r="AQ3">
-        <v>5</v>
-      </c>
-      <c r="AR3" t="s">
+      <c r="AI3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AJ3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AK3" s="3">
+        <v>5</v>
+      </c>
+      <c r="AL3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AM3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AN3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AO3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AP3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AQ3" s="3">
+        <v>5</v>
+      </c>
+      <c r="AR3" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="AS3">
-        <v>5</v>
-      </c>
-      <c r="AT3">
-        <v>5</v>
-      </c>
-      <c r="AU3">
-        <v>4</v>
-      </c>
-      <c r="AV3">
-        <v>4</v>
-      </c>
-      <c r="AW3">
-        <v>4</v>
-      </c>
-      <c r="AX3">
-        <v>4</v>
-      </c>
-      <c r="AY3">
+      <c r="AS3" s="3">
+        <v>5</v>
+      </c>
+      <c r="AT3" s="3">
+        <v>5</v>
+      </c>
+      <c r="AU3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AV3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AW3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AX3" s="3">
+        <v>4</v>
+      </c>
+      <c r="AY3" s="3">
         <v>3</v>
       </c>
-      <c r="AZ3">
-        <v>4</v>
-      </c>
-      <c r="BA3">
+      <c r="AZ3" s="3">
+        <v>4</v>
+      </c>
+      <c r="BA3" s="3">
         <v>3</v>
       </c>
-      <c r="BB3">
+      <c r="BB3" s="3">
         <v>3</v>
       </c>
-      <c r="BC3">
+      <c r="BC3" s="3">
         <v>3</v>
       </c>
-      <c r="BD3">
+      <c r="BD3" s="3">
         <v>3</v>
       </c>
-      <c r="BE3" t="s">
+      <c r="BE3" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="BF3" t="s">
+      <c r="BF3" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:58">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>117.283042</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>31.86119</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="3">
         <v>1</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="3">
         <v>1</v>
       </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
+      <c r="Q4" s="3">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3">
         <v>1</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>4</v>
-      </c>
-      <c r="Y4">
-        <v>4</v>
-      </c>
-      <c r="Z4">
+      <c r="S4" s="3">
+        <v>0</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0</v>
+      </c>
+      <c r="U4" s="3">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3">
+        <v>0</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0</v>
+      </c>
+      <c r="X4" s="3">
+        <v>4</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>4</v>
+      </c>
+      <c r="Z4" s="3">
         <v>3</v>
       </c>
-      <c r="AA4">
-        <v>4</v>
-      </c>
-      <c r="AB4">
+      <c r="AA4" s="3">
+        <v>4</v>
+      </c>
+      <c r="AB4" s="3">
         <v>2</v>
       </c>
-      <c r="AC4">
-        <v>5</v>
-      </c>
-      <c r="AD4">
+      <c r="AC4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD4" s="3">
         <v>3</v>
       </c>
-      <c r="AE4">
-        <v>4</v>
-      </c>
-      <c r="AF4">
-        <v>5</v>
-      </c>
-      <c r="AG4">
-        <v>5</v>
-      </c>
-      <c r="AH4">
-        <v>5</v>
-      </c>
-      <c r="AI4">
+      <c r="AE4" s="3">
+        <v>4</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AG4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AH4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AI4" s="3">
         <v>6</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ4" s="3">
         <v>6</v>
       </c>
-      <c r="AK4">
+      <c r="AK4" s="3">
         <v>6</v>
       </c>
-      <c r="AL4">
-        <v>4</v>
-      </c>
-      <c r="AM4">
-        <v>4</v>
-      </c>
-      <c r="AN4">
-        <v>4</v>
-      </c>
-      <c r="AO4">
-        <v>4</v>
-      </c>
-      <c r="AP4">
-        <v>5</v>
-      </c>
-      <c r="AQ4">
-        <v>5</v>
-      </c>
-      <c r="AR4" t="s">
+      <c r="AL4" s="3">
+        <v>4</v>
+      </c>
+      <c r="AM4" s="3">
+        <v>4</v>
+      </c>
+      <c r="AN4" s="3">
+        <v>4</v>
+      </c>
+      <c r="AO4" s="3">
+        <v>4</v>
+      </c>
+      <c r="AP4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AQ4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AR4" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="AS4">
-        <v>5</v>
-      </c>
-      <c r="AT4">
-        <v>5</v>
-      </c>
-      <c r="AU4">
-        <v>5</v>
-      </c>
-      <c r="AV4">
-        <v>5</v>
-      </c>
-      <c r="AW4">
-        <v>5</v>
-      </c>
-      <c r="AX4">
-        <v>5</v>
-      </c>
-      <c r="AY4">
-        <v>4</v>
-      </c>
-      <c r="AZ4">
-        <v>4</v>
-      </c>
-      <c r="BA4">
-        <v>5</v>
-      </c>
-      <c r="BB4">
-        <v>4</v>
-      </c>
-      <c r="BC4">
+      <c r="AS4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AT4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AU4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AV4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AW4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AX4" s="3">
+        <v>5</v>
+      </c>
+      <c r="AY4" s="3">
+        <v>4</v>
+      </c>
+      <c r="AZ4" s="3">
+        <v>4</v>
+      </c>
+      <c r="BA4" s="3">
+        <v>5</v>
+      </c>
+      <c r="BB4" s="3">
+        <v>4</v>
+      </c>
+      <c r="BC4" s="3">
         <v>2</v>
       </c>
-      <c r="BD4">
-        <v>4</v>
-      </c>
-      <c r="BE4" t="s">
+      <c r="BD4" s="3">
+        <v>4</v>
+      </c>
+      <c r="BE4" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BF4" s="3" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:58">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>117.283042</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>31.86119</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="3">
         <v>1</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="3">
         <v>1</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>5</v>
-      </c>
-      <c r="Y5">
-        <v>5</v>
-      </c>
-      <c r="Z5">
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3">
+        <v>0</v>
+      </c>
+      <c r="T5" s="3">
+        <v>0</v>
+      </c>
+      <c r="U5" s="3">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3">
+        <v>0</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0</v>
+      </c>
+      <c r="X5" s="3">
+        <v>5</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>5</v>
+      </c>
+      <c r="Z5" s="3">
         <v>2</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" s="3">
         <v>1</v>
       </c>
-      <c r="AB5">
+      <c r="AB5" s="3">
         <v>1</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="3">
         <v>3</v>
       </c>
-      <c r="AD5">
-        <v>4</v>
-      </c>
-      <c r="AE5">
-        <v>5</v>
-      </c>
-      <c r="AF5">
-        <v>5</v>
-      </c>
-      <c r="AG5">
-        <v>5</v>
-      </c>
-      <c r="AH5">
-        <v>5</v>
-      </c>
-      <c r="AI5">
-        <v>5</v>
-      </c>
-      <c r="AJ5">
+      <c r="AD5" s="3">
+        <v>4</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AG5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AI5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AJ5" s="3">
         <v>6</v>
       </c>
-      <c r="AK5">
-        <v>5</v>
-      </c>
-      <c r="AL5">
-        <v>5</v>
-      </c>
-      <c r="AM5">
-        <v>4</v>
-      </c>
-      <c r="AN5">
+      <c r="AK5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AL5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AM5" s="3">
+        <v>4</v>
+      </c>
+      <c r="AN5" s="3">
         <v>3</v>
       </c>
-      <c r="AO5">
+      <c r="AO5" s="3">
         <v>2</v>
       </c>
-      <c r="AP5">
+      <c r="AP5" s="3">
         <v>2</v>
       </c>
-      <c r="AQ5">
-        <v>5</v>
-      </c>
-      <c r="AR5" t="s">
+      <c r="AQ5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AR5" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AS5">
-        <v>4</v>
-      </c>
-      <c r="AT5">
+      <c r="AS5" s="3">
+        <v>4</v>
+      </c>
+      <c r="AT5" s="3">
         <v>6</v>
       </c>
-      <c r="AU5">
+      <c r="AU5" s="3">
         <v>6</v>
       </c>
-      <c r="AV5">
+      <c r="AV5" s="3">
         <v>6</v>
       </c>
-      <c r="AW5">
-        <v>5</v>
-      </c>
-      <c r="AX5">
-        <v>4</v>
-      </c>
-      <c r="AY5">
-        <v>5</v>
-      </c>
-      <c r="AZ5">
-        <v>5</v>
-      </c>
-      <c r="BA5">
+      <c r="AW5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AX5" s="3">
+        <v>4</v>
+      </c>
+      <c r="AY5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AZ5" s="3">
+        <v>5</v>
+      </c>
+      <c r="BA5" s="3">
         <v>3</v>
       </c>
-      <c r="BB5">
+      <c r="BB5" s="3">
         <v>1</v>
       </c>
-      <c r="BC5">
+      <c r="BC5" s="3">
         <v>1</v>
       </c>
-      <c r="BD5">
+      <c r="BD5" s="3">
         <v>2</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BE5" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BF5" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:58">
+      <c r="A6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="1">
+        <v>117.283042</v>
+      </c>
+      <c r="F6" s="1">
+        <v>31.86119</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>3</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>6</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>6</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>6</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AU6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AZ6" s="1">
+        <v>4</v>
+      </c>
+      <c r="BA6" s="1">
+        <v>5</v>
+      </c>
+      <c r="BB6" s="1">
+        <v>4</v>
+      </c>
+      <c r="BC6" s="1">
+        <v>2</v>
+      </c>
+      <c r="BD6" s="1">
+        <v>4</v>
+      </c>
+      <c r="BE6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="BF6" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:58">
+      <c r="A7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="1">
+        <v>117.283042</v>
+      </c>
+      <c r="F7" s="1">
+        <v>31.86119</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>6</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>6</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>6</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>6</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AZ7" s="1">
+        <v>5</v>
+      </c>
+      <c r="BA7" s="1">
+        <v>3</v>
+      </c>
+      <c r="BB7" s="1">
+        <v>1</v>
+      </c>
+      <c r="BC7" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="1">
+        <v>2</v>
+      </c>
+      <c r="BE7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BF7" s="1" t="s">
         <v>92</v>
       </c>
     </row>

--- a/问卷数据.xlsx
+++ b/问卷数据.xlsx
@@ -32,14 +32,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="113">
   <si>
     <t>作答ID</t>
   </si>
   <si>
+    <t>作答总时长(秒)</t>
+  </si>
+  <si>
     <t>作答渠道</t>
   </si>
   <si>
+    <t>发布ID</t>
+  </si>
+  <si>
     <t>问卷发布名称</t>
   </si>
   <si>
@@ -214,46 +220,115 @@
     <t>匿名作答</t>
   </si>
   <si>
+    <t>m6ryEr</t>
+  </si>
+  <si>
     <t>针对英语专业学生德语二外学习动机的结构重组与动态演变观察（“田野调查部分”）</t>
   </si>
   <si>
+    <t>27.156.135.102</t>
+  </si>
+  <si>
+    <t>福建省</t>
+  </si>
+  <si>
+    <t>宁德市</t>
+  </si>
+  <si>
+    <t>MOBILE</t>
+  </si>
+  <si>
+    <t>Android</t>
+  </si>
+  <si>
+    <t>WeChat</t>
+  </si>
+  <si>
+    <t>360px*782px</t>
+  </si>
+  <si>
+    <t>女</t>
+  </si>
+  <si>
+    <t>偶尔接触（如影视、音乐）</t>
+  </si>
+  <si>
+    <t>2-3小时</t>
+  </si>
+  <si>
+    <t>会，兴趣使然</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>2号</t>
+  </si>
+  <si>
+    <t>39.144.239.130</t>
+  </si>
+  <si>
+    <t>安徽省</t>
+  </si>
+  <si>
+    <t>合肥市</t>
+  </si>
+  <si>
+    <t>393px*873px</t>
+  </si>
+  <si>
+    <t>男</t>
+  </si>
+  <si>
+    <t>从未接触</t>
+  </si>
+  <si>
+    <t>1-2小时</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会 </t>
+  </si>
+  <si>
+    <t>加强对单词的硬性要求</t>
+  </si>
+  <si>
+    <t>3号</t>
+  </si>
+  <si>
+    <t>UJna6n</t>
+  </si>
+  <si>
+    <t>36.60.79.75</t>
+  </si>
+  <si>
+    <t>367px*814px</t>
+  </si>
+  <si>
+    <t>可能吧，德语的发音较为简单</t>
+  </si>
+  <si>
+    <t>多背单词。</t>
+  </si>
+  <si>
+    <t>4号</t>
+  </si>
+  <si>
     <t>39.144.38.53</t>
   </si>
   <si>
-    <t>安徽省</t>
-  </si>
-  <si>
-    <t>合肥市</t>
-  </si>
-  <si>
-    <t>MOBILE</t>
-  </si>
-  <si>
     <t>iOS</t>
   </si>
   <si>
-    <t>WeChat</t>
-  </si>
-  <si>
     <t>440px*956px</t>
   </si>
   <si>
-    <t>女</t>
-  </si>
-  <si>
-    <t>偶尔接触（如影视、音乐）</t>
-  </si>
-  <si>
-    <t>2-3小时</t>
-  </si>
-  <si>
     <t>是的，即使很难但是也确实挺有意思的</t>
   </si>
   <si>
     <t>挺好的</t>
   </si>
   <si>
-    <t>2号</t>
+    <t>5号</t>
   </si>
   <si>
     <t>36.59.242.75</t>
@@ -262,33 +337,21 @@
     <t>393px*852px</t>
   </si>
   <si>
-    <t>从未接触</t>
-  </si>
-  <si>
-    <t>1-2小时</t>
-  </si>
-  <si>
     <t>会，大一学习的专业是德语，有一定基础，相较于其他小语种会更有优势？</t>
   </si>
   <si>
     <t>暂时没有</t>
   </si>
   <si>
-    <t>3号</t>
+    <t>6号</t>
   </si>
   <si>
     <t>220.178.83.35</t>
   </si>
   <si>
-    <t>Android</t>
-  </si>
-  <si>
     <t>361px*801px</t>
   </si>
   <si>
-    <t>男</t>
-  </si>
-  <si>
     <t>3-5小时</t>
   </si>
   <si>
@@ -298,7 +361,7 @@
     <t>希望考试简单一点，现在上课非常好。</t>
   </si>
   <si>
-    <t>4号</t>
+    <t>7号</t>
   </si>
   <si>
     <t>36.60.95.175</t>
@@ -308,15 +371,6 @@
   </si>
   <si>
     <t>会，因为德语逻辑的严谨性以及德语发音与汉语拼音的相似</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>5号</t>
-  </si>
-  <si>
-    <t>6号</t>
   </si>
 </sst>
 </file>
@@ -932,17 +986,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1478,1246 +1526,1466 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BF7"/>
-  <sheetFormatPr defaultColWidth="9.55752212389381" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:BH8"/>
+  <sheetFormatPr defaultColWidth="40.5575221238938" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="9.55752212389381" style="2"/>
-    <col min="2" max="2" width="9.55752212389381" style="3"/>
-    <col min="3" max="3" width="21.1858407079646" style="3" customWidth="1"/>
-    <col min="4" max="5" width="11.6637168141593" style="3"/>
-    <col min="6" max="16384" width="9.55752212389381" style="3"/>
+    <col min="1" max="16384" width="40.5575221238938" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:60">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BA1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BB1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BC1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BD1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BE1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BF1" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="2" spans="1:58">
-      <c r="A2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:60">
+      <c r="A2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="1">
+        <v>255</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="3">
+      <c r="D2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="1">
+        <v>119.527082</v>
+      </c>
+      <c r="H2" s="1">
+        <v>26.65924</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2" s="1">
+        <v>1</v>
+      </c>
+      <c r="W2" s="1">
+        <v>0</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>6</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>4</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>6</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>6</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>6</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>4</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>2</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>6</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>6</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>6</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>2</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>5</v>
+      </c>
+      <c r="AZ2" s="1">
+        <v>3</v>
+      </c>
+      <c r="BA2" s="1">
+        <v>4</v>
+      </c>
+      <c r="BB2" s="1">
+        <v>5</v>
+      </c>
+      <c r="BC2" s="1">
+        <v>1</v>
+      </c>
+      <c r="BD2" s="1">
+        <v>1</v>
+      </c>
+      <c r="BE2" s="1">
+        <v>1</v>
+      </c>
+      <c r="BF2" s="1">
+        <v>1</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:60">
+      <c r="A3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="1">
+        <v>276</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="1">
         <v>117.283042</v>
       </c>
-      <c r="F2" s="3">
+      <c r="H3" s="1">
         <v>31.86119</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>0</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>2</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>5</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>5</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>5</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>5</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AW3" s="1">
+        <v>3</v>
+      </c>
+      <c r="AX3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AY3" s="1">
+        <v>4</v>
+      </c>
+      <c r="AZ3" s="1">
+        <v>4</v>
+      </c>
+      <c r="BA3" s="1">
+        <v>3</v>
+      </c>
+      <c r="BB3" s="1">
+        <v>5</v>
+      </c>
+      <c r="BC3" s="1">
+        <v>3</v>
+      </c>
+      <c r="BD3" s="1">
+        <v>2</v>
+      </c>
+      <c r="BE3" s="1">
+        <v>1</v>
+      </c>
+      <c r="BF3" s="1">
+        <v>3</v>
+      </c>
+      <c r="BG3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:60">
+      <c r="A4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="1">
+        <v>231</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="F4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="1">
+        <v>117.283042</v>
+      </c>
+      <c r="H4" s="1">
+        <v>31.86119</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="L4" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="M4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="3">
-        <v>1</v>
-      </c>
-      <c r="P2" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0</v>
-      </c>
-      <c r="S2" s="3">
-        <v>0</v>
-      </c>
-      <c r="T2" s="3">
-        <v>0</v>
-      </c>
-      <c r="U2" s="3">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3">
-        <v>0</v>
-      </c>
-      <c r="W2" s="3">
-        <v>0</v>
-      </c>
-      <c r="X2" s="3">
-        <v>5</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>4</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>4</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>4</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>3</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>4</v>
-      </c>
-      <c r="AD2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AE2" s="3">
-        <v>3</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>4</v>
-      </c>
-      <c r="AG2" s="3">
-        <v>4</v>
-      </c>
-      <c r="AH2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AI2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AJ2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AK2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AL2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AM2" s="3">
-        <v>4</v>
-      </c>
-      <c r="AN2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AO2" s="3">
-        <v>4</v>
-      </c>
-      <c r="AP2" s="3">
-        <v>4</v>
-      </c>
-      <c r="AQ2" s="3">
+      <c r="N4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
+        <v>1</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF4" s="1">
         <v>6</v>
       </c>
-      <c r="AR2" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AS2" s="3">
-        <v>4</v>
-      </c>
-      <c r="AT2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AU2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AV2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AW2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AX2" s="3">
-        <v>4</v>
-      </c>
-      <c r="AY2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AZ2" s="3">
-        <v>5</v>
-      </c>
-      <c r="BA2" s="3">
-        <v>3</v>
-      </c>
-      <c r="BB2" s="3">
-        <v>3</v>
-      </c>
-      <c r="BC2" s="3">
-        <v>3</v>
-      </c>
-      <c r="BD2" s="3">
-        <v>4</v>
-      </c>
-      <c r="BE2" s="3" t="s">
+      <c r="AG4" s="1">
+        <v>5</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>5</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>5</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>6</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>3</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>5</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU4" s="1">
+        <v>6</v>
+      </c>
+      <c r="AV4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AW4" s="1">
+        <v>4</v>
+      </c>
+      <c r="AX4" s="1">
+        <v>5</v>
+      </c>
+      <c r="AY4" s="1">
+        <v>6</v>
+      </c>
+      <c r="AZ4" s="1">
+        <v>4</v>
+      </c>
+      <c r="BA4" s="1">
+        <v>4</v>
+      </c>
+      <c r="BB4" s="1">
+        <v>4</v>
+      </c>
+      <c r="BC4" s="1">
+        <v>4</v>
+      </c>
+      <c r="BD4" s="1">
+        <v>1</v>
+      </c>
+      <c r="BE4" s="1">
+        <v>4</v>
+      </c>
+      <c r="BF4" s="1">
+        <v>5</v>
+      </c>
+      <c r="BG4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BH4" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:60">
+      <c r="A5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="1">
+        <v>219</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="1">
+        <v>117.283042</v>
+      </c>
+      <c r="H5" s="1">
+        <v>31.86119</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BF2" s="3" t="s">
+      <c r="P5" s="1" t="s">
         <v>72</v>
       </c>
+      <c r="Q5" s="1">
+        <v>1</v>
+      </c>
+      <c r="R5" s="1">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>4</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>4</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>3</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>4</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>4</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>4</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>4</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>6</v>
+      </c>
+      <c r="AT5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU5" s="1">
+        <v>4</v>
+      </c>
+      <c r="AV5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AW5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AX5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AY5" s="1">
+        <v>5</v>
+      </c>
+      <c r="AZ5" s="1">
+        <v>4</v>
+      </c>
+      <c r="BA5" s="1">
+        <v>5</v>
+      </c>
+      <c r="BB5" s="1">
+        <v>5</v>
+      </c>
+      <c r="BC5" s="1">
+        <v>3</v>
+      </c>
+      <c r="BD5" s="1">
+        <v>3</v>
+      </c>
+      <c r="BE5" s="1">
+        <v>3</v>
+      </c>
+      <c r="BF5" s="1">
+        <v>4</v>
+      </c>
+      <c r="BG5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="BH5" s="1" t="s">
+        <v>97</v>
+      </c>
     </row>
-    <row r="3" spans="1:58">
-      <c r="A3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="3">
+    <row r="6" s="1" customFormat="1" spans="1:60">
+      <c r="A6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="1">
+        <v>297</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="1">
         <v>117.283042</v>
       </c>
-      <c r="F3" s="3">
+      <c r="H6" s="1">
         <v>31.86119</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="O3" s="3">
-        <v>1</v>
-      </c>
-      <c r="P3" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>0</v>
-      </c>
-      <c r="R3" s="3">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3">
-        <v>0</v>
-      </c>
-      <c r="T3" s="3">
-        <v>0</v>
-      </c>
-      <c r="U3" s="3">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3">
-        <v>0</v>
-      </c>
-      <c r="W3" s="3">
-        <v>0</v>
-      </c>
-      <c r="X3" s="3">
-        <v>4</v>
-      </c>
-      <c r="Y3" s="3">
+      <c r="I6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA6" s="1">
         <v>2</v>
       </c>
-      <c r="Z3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AA3" s="3">
+      <c r="AB6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC6" s="1">
         <v>2</v>
       </c>
-      <c r="AB3" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AD3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AE3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AF3" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AH3" s="3">
-        <v>6</v>
-      </c>
-      <c r="AI3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AJ3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AK3" s="3">
-        <v>5</v>
-      </c>
-      <c r="AL3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AM3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AN3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AO3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AP3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AQ3" s="3">
-        <v>5</v>
-      </c>
-      <c r="AR3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AS3" s="3">
-        <v>5</v>
-      </c>
-      <c r="AT3" s="3">
-        <v>5</v>
-      </c>
-      <c r="AU3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AV3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AW3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AX3" s="3">
-        <v>4</v>
-      </c>
-      <c r="AY3" s="3">
-        <v>3</v>
-      </c>
-      <c r="AZ3" s="3">
-        <v>4</v>
-      </c>
-      <c r="BA3" s="3">
-        <v>3</v>
-      </c>
-      <c r="BB3" s="3">
-        <v>3</v>
-      </c>
-      <c r="BC3" s="3">
-        <v>3</v>
-      </c>
-      <c r="BD3" s="3">
-        <v>3</v>
-      </c>
-      <c r="BE3" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="BF3" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:58">
-      <c r="A4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="3">
-        <v>117.283042</v>
-      </c>
-      <c r="F4" s="3">
-        <v>31.86119</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="O4" s="3">
-        <v>1</v>
-      </c>
-      <c r="P4" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>0</v>
-      </c>
-      <c r="R4" s="3">
-        <v>1</v>
-      </c>
-      <c r="S4" s="3">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3">
-        <v>0</v>
-      </c>
-      <c r="U4" s="3">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3">
-        <v>0</v>
-      </c>
-      <c r="W4" s="3">
-        <v>0</v>
-      </c>
-      <c r="X4" s="3">
-        <v>4</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>4</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>3</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>4</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>2</v>
-      </c>
-      <c r="AC4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AD4" s="3">
-        <v>3</v>
-      </c>
-      <c r="AE4" s="3">
-        <v>4</v>
-      </c>
-      <c r="AF4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AH4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AI4" s="3">
-        <v>6</v>
-      </c>
-      <c r="AJ4" s="3">
-        <v>6</v>
-      </c>
-      <c r="AK4" s="3">
-        <v>6</v>
-      </c>
-      <c r="AL4" s="3">
-        <v>4</v>
-      </c>
-      <c r="AM4" s="3">
-        <v>4</v>
-      </c>
-      <c r="AN4" s="3">
-        <v>4</v>
-      </c>
-      <c r="AO4" s="3">
-        <v>4</v>
-      </c>
-      <c r="AP4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AQ4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AR4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AT4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AU4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AV4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AW4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AX4" s="3">
-        <v>5</v>
-      </c>
-      <c r="AY4" s="3">
-        <v>4</v>
-      </c>
-      <c r="AZ4" s="3">
-        <v>4</v>
-      </c>
-      <c r="BA4" s="3">
-        <v>5</v>
-      </c>
-      <c r="BB4" s="3">
-        <v>4</v>
-      </c>
-      <c r="BC4" s="3">
-        <v>2</v>
-      </c>
-      <c r="BD4" s="3">
-        <v>4</v>
-      </c>
-      <c r="BE4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="BF4" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:58">
-      <c r="A5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="3">
-        <v>117.283042</v>
-      </c>
-      <c r="F5" s="3">
-        <v>31.86119</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="O5" s="3">
-        <v>1</v>
-      </c>
-      <c r="P5" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3">
-        <v>0</v>
-      </c>
-      <c r="T5" s="3">
-        <v>0</v>
-      </c>
-      <c r="U5" s="3">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3">
-        <v>0</v>
-      </c>
-      <c r="X5" s="3">
-        <v>5</v>
-      </c>
-      <c r="Y5" s="3">
-        <v>5</v>
-      </c>
-      <c r="Z5" s="3">
-        <v>2</v>
-      </c>
-      <c r="AA5" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="3">
-        <v>3</v>
-      </c>
-      <c r="AD5" s="3">
-        <v>4</v>
-      </c>
-      <c r="AE5" s="3">
-        <v>5</v>
-      </c>
-      <c r="AF5" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG5" s="3">
-        <v>5</v>
-      </c>
-      <c r="AH5" s="3">
-        <v>5</v>
-      </c>
-      <c r="AI5" s="3">
-        <v>5</v>
-      </c>
-      <c r="AJ5" s="3">
-        <v>6</v>
-      </c>
-      <c r="AK5" s="3">
-        <v>5</v>
-      </c>
-      <c r="AL5" s="3">
-        <v>5</v>
-      </c>
-      <c r="AM5" s="3">
-        <v>4</v>
-      </c>
-      <c r="AN5" s="3">
-        <v>3</v>
-      </c>
-      <c r="AO5" s="3">
-        <v>2</v>
-      </c>
-      <c r="AP5" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ5" s="3">
-        <v>5</v>
-      </c>
-      <c r="AR5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AS5" s="3">
-        <v>4</v>
-      </c>
-      <c r="AT5" s="3">
-        <v>6</v>
-      </c>
-      <c r="AU5" s="3">
-        <v>6</v>
-      </c>
-      <c r="AV5" s="3">
-        <v>6</v>
-      </c>
-      <c r="AW5" s="3">
-        <v>5</v>
-      </c>
-      <c r="AX5" s="3">
-        <v>4</v>
-      </c>
-      <c r="AY5" s="3">
-        <v>5</v>
-      </c>
-      <c r="AZ5" s="3">
-        <v>5</v>
-      </c>
-      <c r="BA5" s="3">
-        <v>3</v>
-      </c>
-      <c r="BB5" s="3">
-        <v>1</v>
-      </c>
-      <c r="BC5" s="3">
-        <v>1</v>
-      </c>
-      <c r="BD5" s="3">
-        <v>2</v>
-      </c>
-      <c r="BE5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="BF5" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:58">
-      <c r="A6" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="1">
-        <v>117.283042</v>
-      </c>
-      <c r="F6" s="1">
-        <v>31.86119</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="1">
-        <v>1</v>
-      </c>
-      <c r="P6" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>1</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
-      <c r="T6" s="1">
-        <v>0</v>
-      </c>
-      <c r="U6" s="1">
-        <v>0</v>
-      </c>
-      <c r="V6" s="1">
-        <v>0</v>
-      </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
-      <c r="X6" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>4</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>3</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>4</v>
-      </c>
-      <c r="AB6" s="1">
-        <v>2</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>5</v>
-      </c>
       <c r="AD6" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="1">
         <v>4</v>
       </c>
       <c r="AF6" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG6" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH6" s="1">
         <v>5</v>
       </c>
       <c r="AI6" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ6" s="1">
         <v>6</v>
       </c>
       <c r="AK6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AT6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>5</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>4</v>
+      </c>
+      <c r="AZ6" s="1">
+        <v>4</v>
+      </c>
+      <c r="BA6" s="1">
+        <v>3</v>
+      </c>
+      <c r="BB6" s="1">
+        <v>4</v>
+      </c>
+      <c r="BC6" s="1">
+        <v>3</v>
+      </c>
+      <c r="BD6" s="1">
+        <v>3</v>
+      </c>
+      <c r="BE6" s="1">
+        <v>3</v>
+      </c>
+      <c r="BF6" s="1">
+        <v>3</v>
+      </c>
+      <c r="BG6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="BH6" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:60">
+      <c r="A7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="1">
+        <v>267</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="1">
+        <v>117.283042</v>
+      </c>
+      <c r="H7" s="1">
+        <v>31.86119</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>1</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>2</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>3</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AK7" s="1">
         <v>6</v>
       </c>
-      <c r="AL6" s="1">
-        <v>4</v>
-      </c>
-      <c r="AM6" s="1">
-        <v>4</v>
-      </c>
-      <c r="AN6" s="1">
-        <v>4</v>
-      </c>
-      <c r="AO6" s="1">
-        <v>4</v>
-      </c>
-      <c r="AP6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AQ6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AR6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AT6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AU6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AV6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AW6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AX6" s="1">
-        <v>5</v>
-      </c>
-      <c r="AY6" s="1">
-        <v>4</v>
-      </c>
-      <c r="AZ6" s="1">
-        <v>4</v>
-      </c>
-      <c r="BA6" s="1">
-        <v>5</v>
-      </c>
-      <c r="BB6" s="1">
-        <v>4</v>
-      </c>
-      <c r="BC6" s="1">
+      <c r="AL7" s="1">
+        <v>6</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>6</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>4</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AT7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>5</v>
+      </c>
+      <c r="AZ7" s="1">
+        <v>5</v>
+      </c>
+      <c r="BA7" s="1">
+        <v>4</v>
+      </c>
+      <c r="BB7" s="1">
+        <v>4</v>
+      </c>
+      <c r="BC7" s="1">
+        <v>5</v>
+      </c>
+      <c r="BD7" s="1">
+        <v>4</v>
+      </c>
+      <c r="BE7" s="1">
         <v>2</v>
       </c>
-      <c r="BD6" s="1">
-        <v>4</v>
-      </c>
-      <c r="BE6" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="BF6" s="1" t="s">
+      <c r="BF7" s="1">
+        <v>4</v>
+      </c>
+      <c r="BG7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="BH7" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:60">
+      <c r="A8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="1">
+        <v>462</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:58">
-      <c r="A7" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="E8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" s="1">
         <v>117.283042</v>
       </c>
-      <c r="F7" s="1">
+      <c r="H8" s="1">
         <v>31.86119</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="N7" s="1" t="s">
+      <c r="I8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="O7" s="1">
-        <v>1</v>
-      </c>
-      <c r="P7" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1">
-        <v>0</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-      <c r="X7" s="1">
-        <v>5</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z7" s="1">
+      <c r="N8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>1</v>
+      </c>
+      <c r="R8" s="1">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AB8" s="1">
         <v>2</v>
       </c>
-      <c r="AA7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>3</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>4</v>
-      </c>
-      <c r="AE7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AF7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AG7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AH7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AI7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AJ7" s="1">
+      <c r="AC8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL8" s="1">
         <v>6</v>
       </c>
-      <c r="AK7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AL7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AM7" s="1">
-        <v>4</v>
-      </c>
-      <c r="AN7" s="1">
-        <v>3</v>
-      </c>
-      <c r="AO7" s="1">
+      <c r="AM8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>3</v>
+      </c>
+      <c r="AQ8" s="1">
         <v>2</v>
       </c>
-      <c r="AP7" s="1">
+      <c r="AR8" s="1">
         <v>2</v>
       </c>
-      <c r="AQ7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AR7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AS7" s="1">
-        <v>4</v>
-      </c>
-      <c r="AT7" s="1">
+      <c r="AS8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AT8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>4</v>
+      </c>
+      <c r="AV8" s="1">
         <v>6</v>
       </c>
-      <c r="AU7" s="1">
+      <c r="AW8" s="1">
         <v>6</v>
       </c>
-      <c r="AV7" s="1">
+      <c r="AX8" s="1">
         <v>6</v>
       </c>
-      <c r="AW7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AX7" s="1">
-        <v>4</v>
-      </c>
-      <c r="AY7" s="1">
-        <v>5</v>
-      </c>
-      <c r="AZ7" s="1">
-        <v>5</v>
-      </c>
-      <c r="BA7" s="1">
-        <v>3</v>
-      </c>
-      <c r="BB7" s="1">
-        <v>1</v>
-      </c>
-      <c r="BC7" s="1">
-        <v>1</v>
-      </c>
-      <c r="BD7" s="1">
+      <c r="AY8" s="1">
+        <v>5</v>
+      </c>
+      <c r="AZ8" s="1">
+        <v>4</v>
+      </c>
+      <c r="BA8" s="1">
+        <v>5</v>
+      </c>
+      <c r="BB8" s="1">
+        <v>5</v>
+      </c>
+      <c r="BC8" s="1">
+        <v>3</v>
+      </c>
+      <c r="BD8" s="1">
+        <v>1</v>
+      </c>
+      <c r="BE8" s="1">
+        <v>1</v>
+      </c>
+      <c r="BF8" s="1">
         <v>2</v>
       </c>
-      <c r="BE7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="BF7" s="1" t="s">
-        <v>92</v>
+      <c r="BG8" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BH8" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
